--- a/Copy of macro data_2007-2022.xlsx
+++ b/Copy of macro data_2007-2022.xlsx
@@ -3,67 +3,61 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet2" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="5PxJ9XnXZe9PrnxYgY3qNurUqzeXep/MY/VyAGfgmQc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="o4vUiLtVx1t48flllXKlB+/btLMtrlUzkZAGOUQJnZc="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
-    <t>Country</t>
+    <t>year</t>
   </si>
   <si>
-    <t>Year</t>
+    <t>food_imp_per_gdp</t>
   </si>
   <si>
-    <t>foodimppergdp</t>
+    <t>tour_arrival</t>
   </si>
   <si>
-    <t>tourarrival</t>
-  </si>
-  <si>
-    <t>agripergdp</t>
+    <t>agri_per_gdp</t>
   </si>
   <si>
     <t>inflation</t>
   </si>
   <si>
-    <t>lag_foodimppergdp</t>
+    <t>lag_food_imp_per_gdp</t>
   </si>
   <si>
-    <t>foodprodindex</t>
+    <t>food_prod_index</t>
   </si>
   <si>
-    <t>gdppercapita</t>
+    <t>gdp_per_capita</t>
   </si>
   <si>
     <t>gdp</t>
   </si>
   <si>
-    <t>gdpchangepercent</t>
+    <t>gdp_change_percent</t>
   </si>
   <si>
-    <t>foodproductsimp</t>
+    <t>food_products_imp</t>
   </si>
   <si>
-    <t>foodanimalimp</t>
+    <t>food_animal_imp</t>
   </si>
   <si>
-    <t>foodvegimp</t>
+    <t>food_veg_imp</t>
   </si>
   <si>
-    <t>totalfoodimp</t>
-  </si>
-  <si>
-    <t>Barbados</t>
+    <t>total_food_imp</t>
   </si>
 </sst>
 </file>
@@ -79,11 +73,11 @@
     </font>
     <font>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -105,15 +99,18 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -327,10 +324,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="9" width="8.63"/>
-    <col customWidth="1" min="10" max="10" width="12.0"/>
-    <col customWidth="1" min="11" max="15" width="11.0"/>
-    <col customWidth="1" min="16" max="29" width="8.63"/>
+    <col customWidth="1" min="1" max="8" width="8.63"/>
+    <col customWidth="1" min="9" max="9" width="12.0"/>
+    <col customWidth="1" min="10" max="14" width="11.0"/>
+    <col customWidth="1" min="15" max="28" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -346,7 +343,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -358,13 +355,13 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -373,762 +370,711 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="1">
+      <c r="A2" s="2">
         <v>2007.0</v>
       </c>
-      <c r="C2" s="1">
+      <c r="B2" s="2">
         <v>5.7102194517587215</v>
       </c>
-      <c r="D2" s="1">
+      <c r="C2" s="2">
         <v>1191000.0</v>
       </c>
-      <c r="E2" s="1">
+      <c r="D2" s="2">
         <v>1.34702258</v>
       </c>
-      <c r="F2" s="1">
+      <c r="E2" s="2">
         <v>4.034229829</v>
       </c>
-      <c r="G2" s="1">
+      <c r="F2" s="2">
         <v>5.970095606137296</v>
       </c>
-      <c r="H2" s="1">
+      <c r="G2" s="2">
         <v>118.73</v>
       </c>
-      <c r="I2" s="1">
+      <c r="H2" s="2">
         <v>17235.4396</v>
       </c>
-      <c r="J2" s="1">
+      <c r="I2" s="2">
         <v>4.67576795E9</v>
       </c>
-      <c r="K2" s="1">
+      <c r="J2" s="2">
         <v>10.870509717134807</v>
       </c>
-      <c r="L2" s="1">
+      <c r="K2" s="2">
         <v>1.42275967E8</v>
       </c>
-      <c r="M2" s="1">
+      <c r="L2" s="2">
         <v>5.8061281E7</v>
       </c>
-      <c r="N2" s="1">
+      <c r="M2" s="2">
         <v>6.6659363E7</v>
       </c>
-      <c r="O2" s="1">
+      <c r="N2" s="2">
         <v>2.66996611E8</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="A3" s="2">
         <v>2008.0</v>
       </c>
-      <c r="C3" s="1">
+      <c r="B3" s="2">
         <v>6.957317456558627</v>
       </c>
-      <c r="D3" s="1">
+      <c r="C3" s="2">
         <v>1165000.0</v>
       </c>
-      <c r="E3" s="1">
+      <c r="D3" s="2">
         <v>1.29586496</v>
       </c>
-      <c r="F3" s="1">
+      <c r="E3" s="2">
         <v>8.10810811</v>
       </c>
-      <c r="G3" s="1">
+      <c r="F3" s="2">
         <v>5.7102194517587215</v>
       </c>
-      <c r="H3" s="1">
+      <c r="G3" s="2">
         <v>110.38</v>
       </c>
-      <c r="I3" s="1">
+      <c r="H3" s="2">
         <v>17565.693</v>
       </c>
-      <c r="J3" s="1">
+      <c r="I3" s="2">
         <v>4.7904104E9</v>
       </c>
-      <c r="K3" s="1">
+      <c r="J3" s="2">
         <v>2.451842162098741</v>
       </c>
-      <c r="L3" s="1">
+      <c r="K3" s="2">
         <v>1.67284239E8</v>
       </c>
-      <c r="M3" s="1">
+      <c r="L3" s="2">
         <v>6.6537433E7</v>
       </c>
-      <c r="N3" s="1">
+      <c r="M3" s="2">
         <v>9.9462387E7</v>
       </c>
-      <c r="O3" s="1">
+      <c r="N3" s="2">
         <v>3.33284059E8</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="A4" s="2">
         <v>2009.0</v>
       </c>
-      <c r="C4" s="1">
+      <c r="B4" s="2">
         <v>6.243573713103867</v>
       </c>
-      <c r="D4" s="1">
+      <c r="C4" s="2">
         <v>1154000.0</v>
       </c>
-      <c r="E4" s="1">
+      <c r="D4" s="2">
         <v>1.43755848</v>
       </c>
-      <c r="F4" s="1">
+      <c r="E4" s="2">
         <v>3.643861893</v>
       </c>
-      <c r="G4" s="1">
+      <c r="F4" s="2">
         <v>6.957317456558627</v>
       </c>
-      <c r="H4" s="1">
+      <c r="G4" s="2">
         <v>115.89</v>
       </c>
-      <c r="I4" s="1">
+      <c r="H4" s="2">
         <v>16294.9099</v>
       </c>
-      <c r="J4" s="1">
+      <c r="I4" s="2">
         <v>4.4668096E9</v>
       </c>
-      <c r="K4" s="1">
+      <c r="J4" s="2">
         <v>-6.7551790552224915</v>
       </c>
-      <c r="L4" s="1">
+      <c r="K4" s="2">
         <v>1.57048622E8</v>
       </c>
-      <c r="M4" s="1">
+      <c r="L4" s="2">
         <v>5.1702748E7</v>
       </c>
-      <c r="N4" s="1">
+      <c r="M4" s="2">
         <v>7.013718E7</v>
       </c>
-      <c r="O4" s="1">
+      <c r="N4" s="2">
         <v>2.7888855E8</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="A5" s="2">
         <v>2010.0</v>
       </c>
-      <c r="C5" s="1">
+      <c r="B5" s="2">
         <v>5.778710751882733</v>
       </c>
-      <c r="D5" s="1">
+      <c r="C5" s="2">
         <v>1197000.0</v>
       </c>
-      <c r="E5" s="1">
+      <c r="D5" s="2">
         <v>1.79955226</v>
       </c>
-      <c r="F5" s="1">
+      <c r="E5" s="2">
         <v>5.824218533</v>
       </c>
-      <c r="G5" s="1">
+      <c r="F5" s="2">
         <v>6.243573713103867</v>
       </c>
-      <c r="H5" s="1">
+      <c r="G5" s="2">
         <v>106.98</v>
       </c>
-      <c r="I5" s="1">
+      <c r="H5" s="2">
         <v>18860.3834</v>
       </c>
-      <c r="J5" s="1">
+      <c r="I5" s="2">
         <v>5.1911885E9</v>
       </c>
-      <c r="K5" s="1">
+      <c r="J5" s="2">
         <v>16.21691911828971</v>
       </c>
-      <c r="L5" s="1">
+      <c r="K5" s="2">
         <v>1.65088003E8</v>
       </c>
-      <c r="M5" s="1">
+      <c r="L5" s="2">
         <v>6.3483737E7</v>
       </c>
-      <c r="N5" s="1">
+      <c r="M5" s="2">
         <v>7.1412028E7</v>
       </c>
-      <c r="O5" s="1">
+      <c r="N5" s="2">
         <v>2.99983768E8</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="A6" s="2">
         <v>2011.0</v>
       </c>
-      <c r="C6" s="1">
+      <c r="B6" s="2">
         <v>6.213502538044461</v>
       </c>
-      <c r="D6" s="1">
+      <c r="C6" s="2">
         <v>1187000.0</v>
       </c>
-      <c r="E6" s="1">
+      <c r="D6" s="2">
         <v>1.69848611</v>
       </c>
-      <c r="F6" s="1">
+      <c r="E6" s="2">
         <v>9.432202402</v>
       </c>
-      <c r="G6" s="1">
+      <c r="F6" s="2">
         <v>5.778710751882733</v>
       </c>
-      <c r="H6" s="1">
+      <c r="G6" s="2">
         <v>108.93</v>
       </c>
-      <c r="I6" s="1">
+      <c r="H6" s="2">
         <v>19345.9953</v>
       </c>
-      <c r="J6" s="1">
+      <c r="I6" s="2">
         <v>5.3421838E9</v>
       </c>
-      <c r="K6" s="1">
+      <c r="J6" s="2">
         <v>2.908684591206811</v>
       </c>
-      <c r="L6" s="1">
+      <c r="K6" s="2">
         <v>1.70617555E8</v>
       </c>
-      <c r="M6" s="1">
+      <c r="L6" s="2">
         <v>7.0213109E7</v>
       </c>
-      <c r="N6" s="1">
+      <c r="M6" s="2">
         <v>9.1106062E7</v>
       </c>
-      <c r="O6" s="1">
+      <c r="N6" s="2">
         <v>3.31936726E8</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="A7" s="2">
         <v>2012.0</v>
       </c>
-      <c r="C7" s="1">
+      <c r="B7" s="2">
         <v>6.4109415258123885</v>
       </c>
-      <c r="D7" s="1">
+      <c r="C7" s="2">
         <v>1053000.0</v>
       </c>
-      <c r="E7" s="1">
+      <c r="D7" s="2">
         <v>1.84899903</v>
       </c>
-      <c r="F7" s="1">
+      <c r="E7" s="2">
         <v>4.533347539</v>
       </c>
-      <c r="G7" s="1">
+      <c r="F7" s="2">
         <v>6.213502538044461</v>
       </c>
-      <c r="H7" s="1">
+      <c r="G7" s="2">
         <v>107.13</v>
       </c>
-      <c r="I7" s="1">
+      <c r="H7" s="2">
         <v>19034.0708</v>
       </c>
-      <c r="J7" s="1">
+      <c r="I7" s="2">
         <v>5.2712575E9</v>
       </c>
-      <c r="K7" s="1">
+      <c r="J7" s="2">
         <v>-1.327664914861222</v>
       </c>
-      <c r="L7" s="1">
+      <c r="K7" s="2">
         <v>1.80314213E8</v>
       </c>
-      <c r="M7" s="1">
+      <c r="L7" s="2">
         <v>6.9331186E7</v>
       </c>
-      <c r="N7" s="1">
+      <c r="M7" s="2">
         <v>8.8291837E7</v>
       </c>
-      <c r="O7" s="1">
+      <c r="N7" s="2">
         <v>3.37937236E8</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1">
+      <c r="A8" s="2">
         <v>2013.0</v>
       </c>
-      <c r="C8" s="1">
+      <c r="B8" s="2">
         <v>6.514381355663558</v>
       </c>
-      <c r="D8" s="1">
+      <c r="C8" s="2">
         <v>1079000.0</v>
       </c>
-      <c r="E8" s="1">
+      <c r="D8" s="2">
         <v>1.97161309</v>
       </c>
-      <c r="F8" s="1">
+      <c r="E8" s="2">
         <v>1.81410436</v>
       </c>
-      <c r="G8" s="1">
+      <c r="F8" s="2">
         <v>6.4109415258123885</v>
       </c>
-      <c r="H8" s="1">
+      <c r="G8" s="2">
         <v>98.01</v>
       </c>
-      <c r="I8" s="1">
+      <c r="H8" s="2">
         <v>19308.0091</v>
       </c>
-      <c r="J8" s="1">
+      <c r="I8" s="2">
         <v>5.36115835E9</v>
       </c>
-      <c r="K8" s="1">
+      <c r="J8" s="2">
         <v>1.705491526452654</v>
       </c>
-      <c r="L8" s="1">
+      <c r="K8" s="2">
         <v>1.90060414E8</v>
       </c>
-      <c r="M8" s="1">
+      <c r="L8" s="2">
         <v>7.036131E7</v>
       </c>
-      <c r="N8" s="1">
+      <c r="M8" s="2">
         <v>8.8824576E7</v>
       </c>
-      <c r="O8" s="1">
+      <c r="N8" s="2">
         <v>3.492463E8</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1">
+      <c r="A9" s="2">
         <v>2014.0</v>
       </c>
-      <c r="C9" s="1">
+      <c r="B9" s="2">
         <v>6.451005033249585</v>
       </c>
-      <c r="D9" s="1">
+      <c r="C9" s="2">
         <v>1079000.0</v>
       </c>
-      <c r="E9" s="1">
+      <c r="D9" s="2">
         <v>1.88337568</v>
       </c>
-      <c r="F9" s="1">
+      <c r="E9" s="2">
         <v>1.769503221</v>
       </c>
-      <c r="G9" s="1">
+      <c r="F9" s="2">
         <v>6.514381355663558</v>
       </c>
-      <c r="H9" s="1">
+      <c r="G9" s="2">
         <v>99.11</v>
       </c>
-      <c r="I9" s="1">
+      <c r="H9" s="2">
         <v>19277.9424</v>
       </c>
-      <c r="J9" s="1">
+      <c r="I9" s="2">
         <v>5.3659767E9</v>
       </c>
-      <c r="K9" s="1">
+      <c r="J9" s="2">
         <v>0.08987516662327275</v>
       </c>
-      <c r="L9" s="1">
+      <c r="K9" s="2">
         <v>1.78706687E8</v>
       </c>
-      <c r="M9" s="1">
+      <c r="L9" s="2">
         <v>8.207809E7</v>
       </c>
-      <c r="N9" s="1">
+      <c r="M9" s="2">
         <v>8.537465E7</v>
       </c>
-      <c r="O9" s="1">
+      <c r="N9" s="2">
         <v>3.46159427E8</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1">
+      <c r="A10" s="2">
         <v>2015.0</v>
       </c>
-      <c r="C10" s="1">
+      <c r="B10" s="2">
         <v>6.626737992791398</v>
       </c>
-      <c r="D10" s="1">
+      <c r="C10" s="2">
         <v>1179000.0</v>
       </c>
-      <c r="E10" s="1">
+      <c r="D10" s="2">
         <v>1.80229026</v>
       </c>
-      <c r="F10" s="1">
+      <c r="E10" s="2">
         <v>-1.11278993</v>
       </c>
-      <c r="G10" s="1">
+      <c r="F10" s="2">
         <v>6.451005033249585</v>
       </c>
-      <c r="H10" s="1">
+      <c r="G10" s="2">
         <v>102.6</v>
       </c>
-      <c r="I10" s="1">
+      <c r="H10" s="2">
         <v>18954.2914</v>
       </c>
-      <c r="J10" s="1">
+      <c r="I10" s="2">
         <v>5.28805775E9</v>
       </c>
-      <c r="K10" s="1">
+      <c r="J10" s="2">
         <v>-1.4520925892205234</v>
       </c>
-      <c r="L10" s="1">
+      <c r="K10" s="2">
         <v>1.90031417E8</v>
       </c>
-      <c r="M10" s="1">
+      <c r="L10" s="2">
         <v>7.6771059E7</v>
       </c>
-      <c r="N10" s="1">
+      <c r="M10" s="2">
         <v>8.3623256E7</v>
       </c>
-      <c r="O10" s="1">
+      <c r="N10" s="2">
         <v>3.50425732E8</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1">
+      <c r="A11" s="2">
         <v>2016.0</v>
       </c>
-      <c r="C11" s="1">
+      <c r="B11" s="2">
         <v>6.474870447683694</v>
       </c>
-      <c r="D11" s="1">
+      <c r="C11" s="2">
         <v>1227000.0</v>
       </c>
-      <c r="E11" s="1">
+      <c r="D11" s="2">
         <v>1.85337592</v>
       </c>
-      <c r="F11" s="1">
+      <c r="E11" s="2">
         <v>1.281928131</v>
       </c>
-      <c r="G11" s="1">
+      <c r="F11" s="2">
         <v>6.626737992791398</v>
       </c>
-      <c r="H11" s="1">
+      <c r="G11" s="2">
         <v>98.24</v>
       </c>
-      <c r="I11" s="1">
+      <c r="H11" s="2">
         <v>19065.807</v>
       </c>
-      <c r="J11" s="1">
+      <c r="I11" s="2">
         <v>5.3307615E9</v>
       </c>
-      <c r="K11" s="1">
+      <c r="J11" s="2">
         <v>0.8075507496112349</v>
       </c>
-      <c r="L11" s="1">
+      <c r="K11" s="2">
         <v>1.89785402E8</v>
       </c>
-      <c r="M11" s="1">
+      <c r="L11" s="2">
         <v>7.0584138E7</v>
       </c>
-      <c r="N11" s="1">
+      <c r="M11" s="2">
         <v>8.4790361E7</v>
       </c>
-      <c r="O11" s="1">
+      <c r="N11" s="2">
         <v>3.45159901E8</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="1">
+      <c r="A12" s="2">
         <v>2017.0</v>
       </c>
-      <c r="C12" s="1">
+      <c r="B12" s="2">
         <v>6.412149734207538</v>
       </c>
-      <c r="D12" s="1">
+      <c r="C12" s="2">
         <v>1345000.0</v>
       </c>
-      <c r="E12" s="1">
+      <c r="D12" s="2">
         <v>1.90604243</v>
       </c>
-      <c r="F12" s="1">
+      <c r="E12" s="2">
         <v>4.66018464</v>
       </c>
-      <c r="G12" s="1">
+      <c r="F12" s="2">
         <v>6.474870447683694</v>
       </c>
-      <c r="H12" s="1">
+      <c r="G12" s="2">
         <v>102.7</v>
       </c>
-      <c r="I12" s="1">
+      <c r="H12" s="2">
         <v>19692.7607</v>
       </c>
-      <c r="J12" s="1">
+      <c r="I12" s="2">
         <v>5.51734045E9</v>
       </c>
-      <c r="K12" s="1">
+      <c r="J12" s="2">
         <v>3.500043098908102</v>
       </c>
-      <c r="L12" s="1">
+      <c r="K12" s="2">
         <v>1.96035138E8</v>
       </c>
-      <c r="M12" s="1">
+      <c r="L12" s="2">
         <v>7.5048139E7</v>
       </c>
-      <c r="N12" s="1">
+      <c r="M12" s="2">
         <v>8.2696854E7</v>
       </c>
-      <c r="O12" s="1">
+      <c r="N12" s="2">
         <v>3.53780131E8</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1">
+      <c r="A13" s="2">
         <v>2018.0</v>
       </c>
-      <c r="C13" s="1">
+      <c r="B13" s="2">
         <v>6.467284788359727</v>
       </c>
-      <c r="D13" s="1">
+      <c r="C13" s="2">
         <v>1356000.0</v>
       </c>
-      <c r="E13" s="1">
+      <c r="D13" s="2">
         <v>2.37119071</v>
       </c>
-      <c r="F13" s="1">
+      <c r="E13" s="2">
         <v>3.673814104</v>
       </c>
-      <c r="G13" s="1">
+      <c r="F13" s="2">
         <v>6.412149734207538</v>
       </c>
-      <c r="H13" s="1">
+      <c r="G13" s="2">
         <v>108.1</v>
       </c>
-      <c r="I13" s="1">
+      <c r="H13" s="2">
         <v>20055.9159</v>
       </c>
-      <c r="J13" s="1">
+      <c r="I13" s="2">
         <v>5.6299162E9</v>
       </c>
-      <c r="K13" s="1">
+      <c r="J13" s="2">
         <v>2.0403988302008806</v>
       </c>
-      <c r="L13" s="1">
+      <c r="K13" s="2">
         <v>1.95790979E8</v>
       </c>
-      <c r="M13" s="1">
+      <c r="L13" s="2">
         <v>8.1144151E7</v>
       </c>
-      <c r="N13" s="1">
+      <c r="M13" s="2">
         <v>8.7167584E7</v>
       </c>
-      <c r="O13" s="1">
+      <c r="N13" s="2">
         <v>3.64102714E8</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1">
+      <c r="A14" s="2">
         <v>2019.0</v>
       </c>
-      <c r="C14" s="1">
+      <c r="B14" s="2">
         <v>6.293704096962695</v>
       </c>
-      <c r="D14" s="1">
+      <c r="C14" s="2">
         <v>966000.0</v>
       </c>
-      <c r="E14" s="1">
+      <c r="D14" s="2">
         <v>2.46990993</v>
       </c>
-      <c r="F14" s="1">
+      <c r="E14" s="2">
         <v>4.100289645</v>
       </c>
-      <c r="G14" s="1">
+      <c r="F14" s="2">
         <v>6.467284788359727</v>
       </c>
-      <c r="H14" s="1">
+      <c r="G14" s="2">
         <v>105.1</v>
       </c>
-      <c r="I14" s="1">
+      <c r="H14" s="2">
         <v>20583.7266</v>
       </c>
-      <c r="J14" s="1">
+      <c r="I14" s="2">
         <v>5.788288E9</v>
       </c>
-      <c r="K14" s="1">
+      <c r="J14" s="2">
         <v>2.813040094628762</v>
       </c>
-      <c r="L14" s="1">
+      <c r="K14" s="2">
         <v>1.94167485E8</v>
       </c>
-      <c r="M14" s="1">
+      <c r="L14" s="2">
         <v>8.1467746E7</v>
       </c>
-      <c r="N14" s="1">
+      <c r="M14" s="2">
         <v>8.8662488E7</v>
       </c>
-      <c r="O14" s="1">
+      <c r="N14" s="2">
         <v>3.64297719E8</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
+      <c r="A15" s="4">
+        <v>2020.0</v>
       </c>
       <c r="B15" s="2">
-        <v>2020.0</v>
-      </c>
-      <c r="C15" s="1">
         <v>6.7810826733887675</v>
       </c>
+      <c r="C15" s="4">
+        <v>490660.0</v>
+      </c>
       <c r="D15" s="2">
-        <v>490660.0</v>
-      </c>
-      <c r="E15" s="1">
         <v>3.317946426732452</v>
       </c>
+      <c r="E15" s="4">
+        <v>3.5</v>
+      </c>
       <c r="F15" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="G15" s="1">
         <v>6.293704096962695</v>
       </c>
-      <c r="H15" s="1">
+      <c r="G15" s="2">
         <v>88.71</v>
       </c>
-      <c r="I15" s="1">
+      <c r="H15" s="2">
         <v>18347.110913105524</v>
       </c>
-      <c r="J15" s="1">
+      <c r="I15" s="2">
         <v>5.16834445E9</v>
       </c>
-      <c r="K15" s="1">
+      <c r="J15" s="2">
         <v>-10.71030933498817</v>
       </c>
-      <c r="L15" s="1">
+      <c r="K15" s="2">
         <v>1.9250662E8</v>
       </c>
-      <c r="M15" s="1">
+      <c r="L15" s="2">
         <v>7.172108E7</v>
       </c>
-      <c r="N15" s="1">
+      <c r="M15" s="2">
         <v>8.624201E7</v>
       </c>
-      <c r="O15" s="1">
+      <c r="N15" s="2">
         <v>3.5046971E8</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="4">
+        <v>2021.0</v>
       </c>
       <c r="B16" s="2">
-        <v>2021.0</v>
-      </c>
-      <c r="C16" s="1">
         <v>7.035158320365603</v>
       </c>
+      <c r="C16" s="4">
+        <v>216786.0</v>
+      </c>
       <c r="D16" s="2">
-        <v>216786.0</v>
-      </c>
-      <c r="E16" s="1">
         <v>2.2907944100877797</v>
       </c>
+      <c r="E16" s="4">
+        <v>2.7</v>
+      </c>
       <c r="F16" s="2">
-        <v>2.7</v>
-      </c>
-      <c r="G16" s="1">
         <v>6.7810826733887675</v>
       </c>
-      <c r="H16" s="1">
+      <c r="G16" s="2">
         <v>89.53</v>
       </c>
-      <c r="I16" s="1">
+      <c r="H16" s="2">
         <v>18696.785895295714</v>
       </c>
-      <c r="J16" s="1">
+      <c r="I16" s="2">
         <v>5.27524205E9</v>
       </c>
-      <c r="K16" s="1">
+      <c r="J16" s="2">
         <v>2.0683141581246582</v>
       </c>
-      <c r="L16" s="1">
+      <c r="K16" s="2">
         <v>1.9712017E8</v>
       </c>
-      <c r="M16" s="1">
+      <c r="L16" s="2">
         <v>7.938377E7</v>
       </c>
-      <c r="N16" s="1">
+      <c r="M16" s="2">
         <v>9.461769E7</v>
       </c>
-      <c r="O16" s="1">
+      <c r="N16" s="2">
         <v>3.7112163E8</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1" t="s">
-        <v>15</v>
+      <c r="A17" s="4">
+        <v>2022.0</v>
       </c>
       <c r="B17" s="2">
-        <v>2022.0</v>
-      </c>
-      <c r="C17" s="1">
         <v>7.4677074557754795</v>
       </c>
+      <c r="C17" s="4">
+        <v>790273.0</v>
+      </c>
       <c r="D17" s="2">
-        <v>790273.0</v>
-      </c>
-      <c r="E17" s="1">
         <v>1.6350197812843823</v>
       </c>
+      <c r="E17" s="4">
+        <v>9.1</v>
+      </c>
       <c r="F17" s="2">
-        <v>9.1</v>
-      </c>
-      <c r="G17" s="1">
         <v>7.035158320365603</v>
       </c>
-      <c r="H17" s="1">
+      <c r="G17" s="2">
         <v>102.71</v>
       </c>
-      <c r="I17" s="1">
+      <c r="H17" s="2">
         <v>22164.026027387557</v>
       </c>
-      <c r="J17" s="1">
+      <c r="I17" s="2">
         <v>6.2573035E9</v>
       </c>
-      <c r="K17" s="1">
+      <c r="J17" s="2">
         <v>18.616424434969765</v>
       </c>
-      <c r="L17" s="1">
+      <c r="K17" s="2">
         <v>2.3368104E8</v>
       </c>
-      <c r="M17" s="1">
+      <c r="L17" s="2">
         <v>1.1051766E8</v>
       </c>
-      <c r="N17" s="1">
+      <c r="M17" s="2">
         <v>1.2307842E8</v>
       </c>
-      <c r="O17" s="1">
+      <c r="N17" s="2">
         <v>4.6727712E8</v>
       </c>
     </row>
